--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N142_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N142_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.40571676640154</v>
+        <v>4.290928974540249</v>
       </c>
       <c r="D2" t="n">
-        <v>26.43230570277053</v>
+        <v>4.295249676700211</v>
       </c>
       <c r="E2" t="n">
-        <v>13.27016173368705</v>
+        <v>2.156401281724146</v>
       </c>
       <c r="F2" t="n">
-        <v>8.893262103951384</v>
+        <v>1.4451550918921</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.89715751601465</v>
+        <v>2.583288096352381</v>
       </c>
       <c r="D3" t="n">
-        <v>15.93479677836895</v>
+        <v>2.589404476484955</v>
       </c>
       <c r="E3" t="n">
-        <v>13.27016173368705</v>
+        <v>2.156401281724146</v>
       </c>
       <c r="F3" t="n">
-        <v>8.893262103951384</v>
+        <v>1.4451550918921</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.18132102669043</v>
+        <v>8.154464666837194</v>
       </c>
       <c r="D4" t="n">
-        <v>27.66156917000767</v>
+        <v>4.495004990126246</v>
       </c>
       <c r="E4" t="n">
-        <v>13.27016173368705</v>
+        <v>2.156401281724146</v>
       </c>
       <c r="F4" t="n">
-        <v>8.893262103951384</v>
+        <v>1.4451550918921</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.57523060658539</v>
+        <v>4.480974973570126</v>
       </c>
       <c r="D5" t="n">
-        <v>29.43574320358411</v>
+        <v>4.783308270582419</v>
       </c>
       <c r="E5" t="n">
-        <v>13.27016173368705</v>
+        <v>2.156401281724146</v>
       </c>
       <c r="F5" t="n">
-        <v>8.893262103951384</v>
+        <v>1.4451550918921</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.99661753654795</v>
+        <v>7.799450349689042</v>
       </c>
       <c r="D6" t="n">
-        <v>43.16537964619332</v>
+        <v>7.014374192506414</v>
       </c>
       <c r="E6" t="n">
-        <v>13.27016173368705</v>
+        <v>2.156401281724146</v>
       </c>
       <c r="F6" t="n">
-        <v>8.893262103951384</v>
+        <v>1.4451550918921</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.11551663904108</v>
+        <v>2.618771453844175</v>
       </c>
       <c r="D7" t="n">
-        <v>28.41605571190735</v>
+        <v>4.617609053184944</v>
       </c>
       <c r="E7" t="n">
-        <v>13.27016173368705</v>
+        <v>2.156401281724146</v>
       </c>
       <c r="F7" t="n">
-        <v>8.893262103951384</v>
+        <v>1.4451550918921</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.16461986274268</v>
+        <v>6.689250727695685</v>
       </c>
       <c r="D8" t="n">
-        <v>42.78867296403568</v>
+        <v>6.953159356655798</v>
       </c>
       <c r="E8" t="n">
-        <v>13.27016173368705</v>
+        <v>2.156401281724146</v>
       </c>
       <c r="F8" t="n">
-        <v>8.893262103951384</v>
+        <v>1.4451550918921</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
